--- a/tests/testdata/excel/保護/書き込みパスワード付き.xlsx
+++ b/tests/testdata/excel/保護/書き込みパスワード付き.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <fileSharing userName="test" algorithmName="SHA-512" hashValue="V329W3/9RP5JoKgIiSadJZRxgnQjJD5syYJZmKBMawnioy2iQG6+95W01+I4RWk3uQbnjsDpXyBpEDApG5zQEg==" saltValue="rCoh8IPZ3Wh5wv9hV/51PA==" spinCount="100000"/>
+  <fileSharing userName="test" algorithmName="SHA-512" hashValue="MpWMAphRy4eY+VF2VQCE3bx/N+C9c3nrqdFFpDgvEkuh0yv0Do/m922V0GXmkcUQRsc9OUBimM/mcTCsg56YeA==" saltValue="WVjuPJIqXFOD/ro2NEmNIA==" spinCount="100000"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E2F7652-A513-450A-B782-676B8A577C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE8DEA10-D2EA-42C6-8686-6B752F7AE897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{15AA6FDA-C479-44B0-8923-0CED522120C5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{C000CC6F-6486-4420-8F15-EC147E927BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="書込保護" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57169AEF-9586-4BFC-A2AF-A95B9D718421}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22363C7E-4A16-4AD5-B54A-89FA7D8A5F68}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/保護/書き込みパスワード付き.xlsx
+++ b/tests/testdata/excel/保護/書き込みパスワード付き.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <fileSharing userName="test" algorithmName="SHA-512" hashValue="MpWMAphRy4eY+VF2VQCE3bx/N+C9c3nrqdFFpDgvEkuh0yv0Do/m922V0GXmkcUQRsc9OUBimM/mcTCsg56YeA==" saltValue="WVjuPJIqXFOD/ro2NEmNIA==" spinCount="100000"/>
+  <fileSharing userName="test" algorithmName="SHA-512" hashValue="IzOq0t7dwg8Ly9GQZcZ4LwqqcPOSHb6RG5DfEnaxbGPw+JfTa4jSLf/8x2ZDaQKrHgkKxCd3xXA02AkuOSw/mg==" saltValue="+xU84G8sxUN6QM5cAkOX/g==" spinCount="100000"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE8DEA10-D2EA-42C6-8686-6B752F7AE897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A184B342-0A39-429C-9909-9ADA0F05058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{C000CC6F-6486-4420-8F15-EC147E927BCA}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{54CBD56B-01CE-4E4C-8B89-C661B56421C6}"/>
   </bookViews>
   <sheets>
     <sheet name="書込保護" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22363C7E-4A16-4AD5-B54A-89FA7D8A5F68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF867A98-F162-4EF5-8170-FBE84D854B93}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
